--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98206</v>
+        <v>98207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
